--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_278_Germany_Baltic_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_278_Germany_Baltic_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3b01c27f651640fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rdacb86de894f4ae1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R6f5a63782d5e4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re8520a5806ca4aa8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R759ad2b812864f0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb61c0feb30014038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rad69f467430f44b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R80a277917dbc4ba2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R3e0efa8813654f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ree6ccffd95564214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1005d224a0664803"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rca5d08a179f84e61"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ278CommercialTable" displayName="EEZ278CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ278CommercialTable" displayName="EEZ278CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ278FunctionalTable" displayName="EEZ278FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ278FunctionalTable" displayName="EEZ278FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ278ValidationTable" displayName="EEZ278ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ278ValidationTable" displayName="EEZ278ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4647,7 +4601,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77bc18a8a08d4e78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a4ce61b51e845d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4657,20 +4611,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4678,660 +4622,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.1441582709</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.1441582709</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$60,A2,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>18.57118278597823</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>18.57118278597823</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6612.023390757601</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.09886475771319</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1255.6388882257484</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6612.023390757601</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1265.3490317665196</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$60,A3,'Species'!$U$2:$U$60))</x:f>
-        <x:v>8366517.395512711</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.09886475771319</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1255.6388882257484</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>8302313.6992935175</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>64203.69621919375</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0077332293797399</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.007733229379739908</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>91.5779562252</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.1042570884699074</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>127.13264671852197</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>91.5779562252</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>137.80171563599308</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$60,A4,'Species'!$U$2:$U$60))</x:f>
-        <x:v>12619.599482270432</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.1042570884699074</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>127.13264671852197</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>11642.547955982622</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>977.0515262878107</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0839207645939517</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.08392076459395166</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5191.566288493899</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.32207892238494</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>209.93213491981393</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5191.566288493899</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>239.64930526375215</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$60,A5,'Species'!$U$2:$U$60))</x:f>
-        <x:v>1244155.2542682793</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.32207892238494</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>209.93213491981393</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1089876.594521259</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>154278.65974702034</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1415560812321042</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.14155608123210411</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6987.2976472195005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.318657007070061</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>208.28452637994047</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6987.2976472195005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>217.07795784768317</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$60,A6,'Species'!$U$2:$U$60))</x:f>
-        <x:v>1516788.3041323305</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.318657007070061</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>208.28452637994047</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1455345.981126786</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>61442.32300554449</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0422183616832978</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.04221836168329776</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5837.2510730245</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0037990038412827</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.087859010538285</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5837.2510730245</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>11.19905532348409</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$60,A7,'Species'!$U$2:$U$60))</x:f>
-        <x:v>65371.69770386825</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0037990038412827</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.087859010538285</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>58885.365833784475</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>6486.331870083777</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1101518480566586</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1101518480566585</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1077.0101306651002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.1020994728175584</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>126.5026061713423</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1077.0101306651002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>237.84831155146102</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$60,A8,'Species'!$U$2:$U$60))</x:f>
-        <x:v>256165.04110251248</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.1020994728175584</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>126.5026061713423</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>136244.58840207307</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>119920.4527004394</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8801850708854628</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8801850708854629</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>336.3118913666</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.0496740253299475</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1121.176600716363</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>336.3118913666</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1569.2311772529793</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$60,A9,'Species'!$U$2:$U$60))</x:f>
-        <x:v>527751.1052133858</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.0496740253299475</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1121.176600716363</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>377065.0231428953</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>150686.08207049046</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.3996289043584542</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.3996289043584543</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>54.42805036760001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.07513202163661</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1188.8635764005724</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>54.42805036760001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1694.7648048632057</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$60,A10,'Species'!$U$2:$U$60))</x:f>
-        <x:v>92242.74416033036</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.07513202163661</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1188.8635764005724</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>64707.52661653543</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>27535.217543794926</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.4255334577532524</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.42553345775325224</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.9008066088999999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.888927721302823</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>774.332916515107</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.9008066088999999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>774.6214263247706</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$60,A11,'Species'!$U$2:$U$60))</x:f>
-        <x:v>697.7841002288977</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.888927721302823</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>774.332916515107</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>697.5242086856202</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0.2598915432774902</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0003725914312955</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0003725914312955773</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.0014561545999999999</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.179999986951935</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1513.5612029623505</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.0014561545999999999</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1773.1382858209292</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$60,A12,'Species'!$U$2:$U$60))</x:f>
-        <x:v>2.5819634713342605</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.179999986951935</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1513.5612029623505</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>2.2039791080751603</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0.37798436325910023</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1715008830502083</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.1715008830502082</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2b8f3f6f53348f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b8069c7b6394902"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5341,20 +4856,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5362,984 +4867,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>6411.181359474501</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.091557603438846</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1234.6890695418904</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>6411.181359474501</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1237.5537462047143</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$60,A2,'Species'!$U$2:$U$60))</x:f>
-        <x:v>7934181.509015502</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.091557603438846</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1234.6890695418904</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>7915815.547393884</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>18365.96162161883</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0023201603816634</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0023201603816634456</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>94.75031030279999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.7147039723674746</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>518.4465303683412</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>94.75031030279999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>623.7833814575295</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$60,A3,'Species'!$U$2:$U$60))</x:f>
-        <x:v>59103.66895483077</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.7147039723674746</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>518.4465303683412</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>49122.969627810344</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>9980.699327020426</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2031778494386867</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.2031778494386866</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1892.742851122</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2991273679736572</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>199.12572405178918</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1892.742851122</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>256.984277787464</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$60,A4,'Species'!$U$2:$U$60))</x:f>
-        <x:v>486405.15463297267</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2991273679736572</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>199.12572405178918</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>376893.79067351605</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>109511.36395945662</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2905629295822514</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.29056292958225133</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>90.55012688999999</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.986810116760953</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>970.085731379712</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>90.55012688999999</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1028.630477127988</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$60,A5,'Species'!$U$2:$U$60))</x:f>
-        <x:v>93142.62022686053</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.986810116760953</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>970.085731379712</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>87841.38607061136</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>5301.234156249164</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0603500740754224</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0603500740754223</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.0009707696999999999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.37</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2344.228815319923</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.0009707696999999999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2344.228815319923</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$60,A6,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2.2757063037794767</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.37</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2344.228815319923</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>2.2757063037794767</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>10.049594443999998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.600895945402193</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>39.89293096161385</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>10.049594443999998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>39.95615374775062</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$60,A7,'Species'!$U$2:$U$60))</x:f>
-        <x:v>401.54314070700434</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.600895945402193</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>39.89293096161385</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>400.9077773467101</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.6353633602942637</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0015848117601989</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0015848117601988884</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>758.1702955183</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3650803766684065</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>231.7823579431179</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>758.1702955183</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>726.7447570799852</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$60,A8,'Species'!$U$2:$U$60))</x:f>
-        <x:v>550996.2872417076</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3650803766684065</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>231.7823579431179</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>175730.49881766207</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>375265.7884240455</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>3.135461920092887</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>2.135461920092887</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>571.3538227345</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.4258256364387223</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>266.5788170514017</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>571.3538227345</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>818.6803167063432</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$60,A9,'Species'!$U$2:$U$60))</x:f>
-        <x:v>467756.1285476603</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.4258256364387223</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>266.5788170514017</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>152310.82618235928</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>315445.30236530106</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>3.0710629065042525</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>2.071062906504253</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5928.3641625138</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.391868322046989</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>246.52917482077305</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5928.3641625138</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>258.043334280322</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$60,A10,'Species'!$U$2:$U$60))</x:f>
-        <x:v>1529774.8553230294</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.391868322046989</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>246.52917482077305</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1461514.7250215705</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>68260.130301459</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.046705058206274</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.046705058206274006</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>0.0788594233</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.53</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>33.88441561392024</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>0.0788594233</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$60,A11,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2.6721054741712655</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
-        <x:v>2.6721054741712655</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>5837.2510730245</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.0037990038412827</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>10.087859010538285</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>5837.2510730245</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>11.19905532348409</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$60,A12,'Species'!$U$2:$U$60))</x:f>
-        <x:v>65371.69770386825</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.0037990038412827</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>10.087859010538285</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>58885.365833784475</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>6486.331870083777</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1101518480566586</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.1101518480566585</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>81.5283617812</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.166303905506102</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>146.6573743764866</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>81.5283617812</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>149.8626499371271</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$60,A13,'Species'!$U$2:$U$60))</x:f>
-        <x:v>12218.056341563428</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.166303905506102</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>146.6573743764866</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>11956.73547604709</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>261.320865516338</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.021855536240627</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.021855536240627027</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>50.51053014319999</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.0800244888145993</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>120.23322293101009</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>50.51053014319999</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>120.23549444288842</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$60,A14,'Species'!$U$2:$U$60))</x:f>
-        <x:v>6073.158566340071</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.0800244888145993</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>120.23322293101009</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>6073.04383107087</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0.1147352692014465</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0000188925475253</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.000018892547525252267</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1158.5813209000003</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.010012442654503</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>102.33223103220489</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1158.5813209000003</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>102.33259599100252</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$60,A15,'Species'!$U$2:$U$60))</x:f>
-        <x:v>118560.63423438177</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.010012442654503</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>102.33223103220489</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>118560.21139993594</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0.42283444582426455</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0000035664110314</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.000003566411031420386</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>4.5752873558</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>4.5752873558</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$60,A16,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>589.4111884976612</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>589.4111884976612</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3298.8234373719</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3352476752323783</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>216.3952259368661</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3298.8234373719</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>229.70313932260336</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$60,A17,'Species'!$U$2:$U$60))</x:f>
-        <x:v>757750.0996353069</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3352476752323783</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>216.3952259368661</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>713849.6430559215</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>43900.456579385325</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0614981838352566</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.06149818383525654</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>0.0004853849</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>0.0004853849</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$60,A18,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>0.306257167554784</x:v>
       </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
-        <x:v>0.306257167554784</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08c7f4b89eca4f45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re036082cc61744d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6514,7 +5380,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6613,7 +5479,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>12082330.078822173</x:v>
+        <x:v>11496799.626263414</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6627,7 +5493,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>12082330.078822175</x:v>
+        <x:v>11129550.316418964</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6641,7 +5507,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.862645149230957e-9</x:v>
+        <x:v>-585530.4525587615</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6655,7 +5521,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-952779.7624032106</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6666,9 +5532,9 @@
         <x:v>EEZ_278</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6680,47 +5546,19 @@
         <x:v>EEZ_278</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_278</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_278</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75a0bc87532e4411"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39c1b401754844bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6767,7 +5605,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
